--- a/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Redundancia/ranking_redundancia.xlsx
+++ b/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Redundancia/ranking_redundancia.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DENSIDAD POBLACIONAL</t>
+          <t>AGUAS RESIDUALES TRATADAS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -498,7 +498,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACCESO A AGUA POTABLE ADECUADO</t>
+          <t>INDICE DE DESEMPENO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -525,7 +525,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
+          <t>ACCESO A AGUA POTABLE ADECUADO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -534,14 +534,14 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COBERTURA DE ACUEDUCTO URBANO</t>
+          <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -561,14 +561,14 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -588,14 +588,14 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -606,7 +606,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>COBERTURA DE ALCANTARILLADO URBANO</t>
+          <t>COBERTURA DE ACUEDUCTO URBANO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -615,14 +615,14 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -642,14 +642,14 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -660,7 +660,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INDICE DE DESEMPENO INSTITUCIONAL</t>
+          <t>COBERTURA DE ALCANTARILLADO URBANO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -669,14 +669,14 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.833</v>
+        <v>0.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -687,7 +687,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CALIDAD DEL AGUA</t>
+          <t>CONDUCTIVIDAD ELECTRICA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -696,14 +696,14 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CONDUCTIVIDAD ELECTRICA</t>
+          <t>DENSIDAD POBLACIONAL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -723,14 +723,14 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -741,7 +741,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+          <t>FOSFORO TOTAL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -750,14 +750,14 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Temp_Max_C</t>
+          <t>POBLACION TOTAL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -780,11 +780,11 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -795,7 +795,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Temp_Media_C</t>
+          <t>Temp_Max_C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -807,11 +807,11 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VolumenUtilDiarioMasa</t>
+          <t>Temp_Media_C</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -834,11 +834,11 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -849,7 +849,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>irca</t>
+          <t>Anio</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AGUAS RESIDUALES TRATADAS</t>
+          <t>CONTINUIDAD DE ACUEDUCTO URBANO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FOSFORO TOTAL</t>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NITROGENO TOTAL</t>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OXIGENO DISUELTO (OD)</t>
+          <t>Humedad_Relativa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SOLIDOS SUSPENDIDOS TOTALES</t>
+          <t>Mes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TEMPERATURA</t>
+          <t>NITROGENO TOTAL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TURBIDEZ</t>
+          <t>Nivel_Minimo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Precipitacion_mm</t>
+          <t>ONI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Temp_Min_C</t>
+          <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humedad_Relativa</t>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Velocidad_Viento</t>
+          <t>Precipitacion_mm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anio</t>
+          <t>SOLIDOS SUSPENDIDOS TOTALES</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mes</t>
+          <t>TEMPERATURA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ONI</t>
+          <t>TURBIDEZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>POBLACION TOTAL</t>
+          <t>Temp_Min_C</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CONTINUIDAD DE ACUEDUCTO URBANO</t>
+          <t>Velocidad_Viento</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nivel_Minimo</t>
+          <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+          <t>irca</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
